--- a/Super Smash Bros Remix-FrameData (version 1.0).xlsx
+++ b/Super Smash Bros Remix-FrameData (version 1.0).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neros\webside\(SSR) Frame Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neros\webside\(SSR) Frame Data\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDB5F44-24B9-4BAF-B2FD-97C621DE6474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8709793-6C21-4B27-8953-15C8445B96D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="839" activeTab="1" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="839" firstSheet="33" activeTab="37" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
   </bookViews>
   <sheets>
     <sheet name="marina" sheetId="13" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="811">
   <si>
     <t>Luigi_OG</t>
   </si>
@@ -2521,6 +2521,21 @@
   </si>
   <si>
     <t>Notes:</t>
+  </si>
+  <si>
+    <t>N-Special(DragonBall)</t>
+  </si>
+  <si>
+    <t>U-Special(Heal-Ground)</t>
+  </si>
+  <si>
+    <t>U-Special(Heal-Air)</t>
+  </si>
+  <si>
+    <t>D-Special(Earthquake-Ground)</t>
+  </si>
+  <si>
+    <t>D-Special(Earthquake-Air)</t>
   </si>
 </sst>
 </file>
@@ -29592,7 +29607,7 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -29839,7 +29854,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>31</v>
+        <v>806</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -29853,7 +29868,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>40</v>
+        <v>807</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -29867,7 +29882,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>117</v>
+        <v>808</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="23"/>
@@ -29881,7 +29896,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>35</v>
+        <v>809</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="23"/>
@@ -29895,7 +29910,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>36</v>
+        <v>810</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>

--- a/Super Smash Bros Remix-FrameData (version 1.0).xlsx
+++ b/Super Smash Bros Remix-FrameData (version 1.0).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neros\webside\(SSR) Frame Data\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8709793-6C21-4B27-8953-15C8445B96D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73085217-3AB4-4D53-9A57-0C5C4B5BDE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="839" firstSheet="33" activeTab="37" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="887" firstSheet="27" activeTab="38" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
   </bookViews>
   <sheets>
     <sheet name="marina" sheetId="13" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="811">
   <si>
     <t>Luigi_OG</t>
   </si>
@@ -30110,7 +30110,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5484D95-5A25-47A1-820B-F3C1C0A12B50}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -30360,11 +30360,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="88" t="s">
-        <v>746</v>
+        <v>482</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -30377,21 +30376,21 @@
         <v>747</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="88" t="s">
         <v>484</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -30401,64 +30400,64 @@
       <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
-        <v>485</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="8"/>
+      <c r="A20" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="88" t="s">
-        <v>482</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="8"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="88" t="s">
-        <v>483</v>
+        <v>43</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="G22" s="2"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+      <c r="A23" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="88" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -30472,7 +30471,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="88" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -30485,78 +30484,78 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="A26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="88" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="2"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="2"/>
+      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+      <c r="A29" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="8"/>
+      <c r="A30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -30566,11 +30565,11 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="88" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -30580,49 +30579,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="88" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="8"/>
+      <c r="J32" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
